--- a/mosip_master/xlsx/doc_type.xlsx
+++ b/mosip_master/xlsx/doc_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthik.SJ\Documents\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9D46DB-3D47-416E-92D1-8BE1A87EBD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11497AE-2BBA-42C1-85B3-657590ED3325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3D55A4D6-22C9-4CF1-9C69-2C07DF02284B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3D55A4D6-22C9-4CF1-9C69-2C07DF02284B}"/>
   </bookViews>
   <sheets>
     <sheet name="doc_type" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="167">
   <si>
     <t>code</t>
   </si>
@@ -497,6 +497,30 @@
   </si>
   <si>
     <t>Welfare and Family</t>
+  </si>
+  <si>
+    <t>MARCER</t>
+  </si>
+  <si>
+    <t>Marriage Certificate</t>
+  </si>
+  <si>
+    <t>jagadeesh_t</t>
+  </si>
+  <si>
+    <t>COBIR</t>
+  </si>
+  <si>
+    <t>Certificate of Citizenship by Birth</t>
+  </si>
+  <si>
+    <t>jivesh</t>
+  </si>
+  <si>
+    <t>COCUA</t>
+  </si>
+  <si>
+    <t>Certificate of Citizenship under Article 9</t>
   </si>
 </sst>
 </file>
@@ -1358,15 +1382,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8DA9DF-E7DB-4477-9DD5-17FD63429B2F}">
-  <dimension ref="A1:K68"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K71"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="25.36328125" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.36328125" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -1427,7 +1454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -1453,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -1479,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -1505,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -1531,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -1557,7 +1584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -1583,7 +1610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -1609,7 +1636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1635,7 +1662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1661,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -1687,7 +1714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -1713,7 +1740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -1739,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -1765,7 +1792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -1791,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1817,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -1843,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1869,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -1895,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>117</v>
       </c>
@@ -1921,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>87</v>
       </c>
@@ -1947,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1973,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -1999,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -2025,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -2051,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -2077,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -2103,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -2129,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -2155,7 +2182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -2181,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -2207,7 +2234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -2233,7 +2260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>121</v>
       </c>
@@ -2259,7 +2286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -2285,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -2311,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -2337,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -2363,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>36</v>
       </c>
@@ -2389,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -2415,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -2441,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -2467,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -2493,7 +2520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>127</v>
       </c>
@@ -2519,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -2545,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>129</v>
       </c>
@@ -2571,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>131</v>
       </c>
@@ -2597,7 +2624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -2623,7 +2650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>133</v>
       </c>
@@ -2649,7 +2676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>136</v>
       </c>
@@ -2675,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -2701,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>138</v>
       </c>
@@ -2727,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -2753,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>89</v>
       </c>
@@ -2779,7 +2806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>142</v>
       </c>
@@ -2805,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -2831,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>67</v>
       </c>
@@ -2857,7 +2884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>143</v>
       </c>
@@ -2883,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>146</v>
       </c>
@@ -2909,7 +2936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>148</v>
       </c>
@@ -2935,7 +2962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -2961,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>31</v>
       </c>
@@ -2987,7 +3014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>60</v>
       </c>
@@ -3013,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>151</v>
       </c>
@@ -3039,7 +3066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -3065,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>153</v>
       </c>
@@ -3091,7 +3118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>155</v>
       </c>
@@ -3117,7 +3144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>157</v>
       </c>
@@ -3140,6 +3167,84 @@
         <v>45516.747916666667</v>
       </c>
       <c r="J68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>159</v>
+      </c>
+      <c r="B69" t="s">
+        <v>160</v>
+      </c>
+      <c r="C69" t="s">
+        <v>160</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
+        <v>161</v>
+      </c>
+      <c r="G69" s="1">
+        <v>45516.747916666667</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>162</v>
+      </c>
+      <c r="B70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" t="s">
+        <v>163</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s">
+        <v>164</v>
+      </c>
+      <c r="G70" s="1">
+        <v>45516.747916666667</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>165</v>
+      </c>
+      <c r="B71" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" t="s">
+        <v>166</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s">
+        <v>164</v>
+      </c>
+      <c r="G71" s="1">
+        <v>45516.747916666667</v>
+      </c>
+      <c r="J71" t="b">
         <v>0</v>
       </c>
     </row>

--- a/mosip_master/xlsx/doc_type.xlsx
+++ b/mosip_master/xlsx/doc_type.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11497AE-2BBA-42C1-85B3-657590ED3325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3131613E-3B50-4409-8A94-14F836BD0E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3D55A4D6-22C9-4CF1-9C69-2C07DF02284B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="169">
   <si>
     <t>code</t>
   </si>
@@ -521,6 +521,12 @@
   </si>
   <si>
     <t>Certificate of Citizenship under Article 9</t>
+  </si>
+  <si>
+    <t>BIBR</t>
+  </si>
+  <si>
+    <t>Certified copy of Birth certificate issued before registration</t>
   </si>
 </sst>
 </file>
@@ -1382,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8DA9DF-E7DB-4477-9DD5-17FD63429B2F}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -3248,6 +3254,32 @@
         <v>0</v>
       </c>
     </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>167</v>
+      </c>
+      <c r="B72" t="s">
+        <v>168</v>
+      </c>
+      <c r="C72" t="s">
+        <v>168</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>164</v>
+      </c>
+      <c r="G72" s="1">
+        <v>45516.747916666667</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/mosip_master/xlsx/doc_type.xlsx
+++ b/mosip_master/xlsx/doc_type.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3131613E-3B50-4409-8A94-14F836BD0E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE73113-BA2A-49D8-8631-397998EE1D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3D55A4D6-22C9-4CF1-9C69-2C07DF02284B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="171">
   <si>
     <t>code</t>
   </si>
@@ -527,6 +527,12 @@
   </si>
   <si>
     <t>Certified copy of Birth certificate issued before registration</t>
+  </si>
+  <si>
+    <t>DNA</t>
+  </si>
+  <si>
+    <t>DNA test results</t>
   </si>
 </sst>
 </file>
@@ -1388,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8DA9DF-E7DB-4477-9DD5-17FD63429B2F}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -3280,6 +3286,32 @@
         <v>0</v>
       </c>
     </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>169</v>
+      </c>
+      <c r="B73" t="s">
+        <v>170</v>
+      </c>
+      <c r="C73" t="s">
+        <v>170</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>95</v>
+      </c>
+      <c r="G73" s="1">
+        <v>45516.747916666667</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/mosip_master/xlsx/doc_type.xlsx
+++ b/mosip_master/xlsx/doc_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nira-registration\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE73113-BA2A-49D8-8631-397998EE1D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659C6299-0D55-4893-930C-E58ECF1D3C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3D55A4D6-22C9-4CF1-9C69-2C07DF02284B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3D55A4D6-22C9-4CF1-9C69-2C07DF02284B}"/>
   </bookViews>
   <sheets>
     <sheet name="doc_type" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="178">
   <si>
     <t>code</t>
   </si>
@@ -379,9 +379,6 @@
     <t>Court Report</t>
   </si>
   <si>
-    <t>Passport Document</t>
-  </si>
-  <si>
     <t>Passport Proof</t>
   </si>
   <si>
@@ -533,6 +530,30 @@
   </si>
   <si>
     <t>DNA test results</t>
+  </si>
+  <si>
+    <t>RECLET</t>
+  </si>
+  <si>
+    <t>Recommendation Letter</t>
+  </si>
+  <si>
+    <t>LFCV</t>
+  </si>
+  <si>
+    <t>Letter for Citizenship Verification</t>
+  </si>
+  <si>
+    <t>LCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letter from LC 1 Chairperson </t>
+  </si>
+  <si>
+    <t>DMG</t>
+  </si>
+  <si>
+    <t>Passport</t>
   </si>
 </sst>
 </file>
@@ -1016,9 +1037,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1394,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8DA9DF-E7DB-4477-9DD5-17FD63429B2F}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2069,10 +2091,10 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" t="s">
         <v>119</v>
-      </c>
-      <c r="C26" t="s">
-        <v>120</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
@@ -2274,13 +2296,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" t="s">
         <v>121</v>
       </c>
-      <c r="B34" t="s">
-        <v>122</v>
-      </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
@@ -2482,13 +2504,13 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" t="s">
         <v>123</v>
       </c>
-      <c r="B42" t="s">
-        <v>124</v>
-      </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
@@ -2508,13 +2530,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" t="s">
         <v>125</v>
       </c>
-      <c r="B43" t="s">
-        <v>126</v>
-      </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
@@ -2534,13 +2556,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
         <v>127</v>
       </c>
-      <c r="B44" t="s">
-        <v>128</v>
-      </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
@@ -2586,13 +2608,13 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" t="s">
         <v>129</v>
       </c>
-      <c r="B46" t="s">
-        <v>130</v>
-      </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
@@ -2612,13 +2634,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" t="s">
         <v>131</v>
       </c>
-      <c r="B47" t="s">
-        <v>132</v>
-      </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -2664,13 +2686,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" t="s">
         <v>133</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>134</v>
-      </c>
-      <c r="C49" t="s">
-        <v>135</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -2690,13 +2712,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>135</v>
+      </c>
+      <c r="B50" t="s">
         <v>136</v>
       </c>
-      <c r="B50" t="s">
-        <v>137</v>
-      </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -2742,13 +2764,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" t="s">
         <v>138</v>
       </c>
-      <c r="B52" t="s">
-        <v>139</v>
-      </c>
       <c r="C52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
@@ -2768,13 +2790,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" t="s">
         <v>140</v>
       </c>
-      <c r="B53" t="s">
-        <v>141</v>
-      </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -2820,13 +2842,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
@@ -2898,13 +2920,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s">
         <v>143</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>144</v>
-      </c>
-      <c r="C58" t="s">
-        <v>145</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
@@ -2924,13 +2946,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" t="s">
         <v>146</v>
-      </c>
-      <c r="B59" t="s">
-        <v>119</v>
-      </c>
-      <c r="C59" t="s">
-        <v>147</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -2950,13 +2972,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>147</v>
+      </c>
+      <c r="B60" t="s">
         <v>148</v>
       </c>
-      <c r="B60" t="s">
-        <v>149</v>
-      </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
@@ -3031,10 +3053,10 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -3054,13 +3076,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B64" t="s">
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -3106,13 +3128,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" t="s">
         <v>153</v>
       </c>
-      <c r="B66" t="s">
-        <v>154</v>
-      </c>
       <c r="C66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
@@ -3132,13 +3154,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" t="s">
         <v>155</v>
       </c>
-      <c r="B67" t="s">
-        <v>156</v>
-      </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
@@ -3158,13 +3180,13 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>156</v>
+      </c>
+      <c r="B68" t="s">
         <v>157</v>
       </c>
-      <c r="B68" t="s">
-        <v>158</v>
-      </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
@@ -3184,22 +3206,22 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" t="s">
         <v>159</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
         <v>160</v>
-      </c>
-      <c r="C69" t="s">
-        <v>160</v>
-      </c>
-      <c r="D69" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" t="s">
-        <v>14</v>
-      </c>
-      <c r="F69" t="s">
-        <v>161</v>
       </c>
       <c r="G69" s="1">
         <v>45516.747916666667</v>
@@ -3210,22 +3232,22 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>161</v>
+      </c>
+      <c r="B70" t="s">
         <v>162</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
+        <v>162</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s">
         <v>163</v>
-      </c>
-      <c r="C70" t="s">
-        <v>163</v>
-      </c>
-      <c r="D70" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" t="s">
-        <v>164</v>
       </c>
       <c r="G70" s="1">
         <v>45516.747916666667</v>
@@ -3236,13 +3258,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" t="s">
         <v>165</v>
       </c>
-      <c r="B71" t="s">
-        <v>166</v>
-      </c>
       <c r="C71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -3251,7 +3273,7 @@
         <v>14</v>
       </c>
       <c r="F71" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G71" s="1">
         <v>45516.747916666667</v>
@@ -3262,13 +3284,13 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" t="s">
         <v>167</v>
       </c>
-      <c r="B72" t="s">
-        <v>168</v>
-      </c>
       <c r="C72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -3277,7 +3299,7 @@
         <v>14</v>
       </c>
       <c r="F72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G72" s="1">
         <v>45516.747916666667</v>
@@ -3288,13 +3310,13 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>168</v>
+      </c>
+      <c r="B73" t="s">
         <v>169</v>
       </c>
-      <c r="B73" t="s">
-        <v>170</v>
-      </c>
       <c r="C73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D73" t="s">
         <v>13</v>
@@ -3309,6 +3331,134 @@
         <v>45516.747916666667</v>
       </c>
       <c r="J73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" t="s">
+        <v>171</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" t="s">
+        <v>95</v>
+      </c>
+      <c r="G74" s="1">
+        <v>45517.747916666667</v>
+      </c>
+      <c r="H74" t="s">
+        <v>95</v>
+      </c>
+      <c r="I74" s="2">
+        <v>45777.484220902777</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>172</v>
+      </c>
+      <c r="B75" t="s">
+        <v>173</v>
+      </c>
+      <c r="C75" t="s">
+        <v>173</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" t="s">
+        <v>95</v>
+      </c>
+      <c r="G75" s="1">
+        <v>45518.747916666667</v>
+      </c>
+      <c r="H75" t="s">
+        <v>95</v>
+      </c>
+      <c r="I75" s="2">
+        <v>45777.483862847221</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>174</v>
+      </c>
+      <c r="B76" t="s">
+        <v>175</v>
+      </c>
+      <c r="C76" t="s">
+        <v>175</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" t="s">
+        <v>95</v>
+      </c>
+      <c r="G76" s="1">
+        <v>45519.747916666667</v>
+      </c>
+      <c r="H76" t="s">
+        <v>95</v>
+      </c>
+      <c r="I76" s="2">
+        <v>45777.478348958335</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" t="s">
+        <v>64</v>
+      </c>
+      <c r="C77" t="s">
+        <v>64</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" t="s">
+        <v>95</v>
+      </c>
+      <c r="G77" s="1">
+        <v>45520.747916666667</v>
+      </c>
+      <c r="H77" t="s">
+        <v>95</v>
+      </c>
+      <c r="I77" s="2">
+        <v>45777.228097662039</v>
+      </c>
+      <c r="J77" t="b">
         <v>0</v>
       </c>
     </row>
